--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/exercise-controller/archiveExercise-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/exercise-controller/archiveExercise-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
-  <si>
-    <t>Statement: exercise-controller.archiveExercise(id) – Server Action. No input validation. Delegates to exerciseService.archiveExercise(). Returns ActionResult&lt;Exercise&gt; with isActive=false.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
+  <si>
+    <t>Statement: archiveExercise(id) – Archives the exercise with the given id and returns an ActionResult&lt;Exercise&gt;. Returns success with the archived exercise (isActive: false) on success. Returns a failure with the service error message for NotFoundError.</t>
   </si>
   <si>
     <t/>
@@ -37,21 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>exerciseService.archiveExercise is mock-injected</t>
+    <t>A known exercise id exists in the store with isActive: true. A non-existent id has no matching record.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;Exercise&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;Exercise&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: Exercise with isActive=false returned.
-On NotFoundError: failure.
-On error: generic failure.</t>
+    <t>On success: exercise archived successfully, returned data has isActive: false and id matches the requested id. On NotFoundError: operation fails with the service error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,16 +64,13 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>exercise existence</t>
-  </si>
-  <si>
-    <t>service resolves Exercise(isActive=false)</t>
-  </si>
-  <si>
-    <t>service throws NotFoundError → failure</t>
-  </si>
-  <si>
-    <t>service throws Error → generic failure</t>
+    <t>ID existence</t>
+  </si>
+  <si>
+    <t>Known existing id → exercise archived successfully, returned data has isActive: false and id matches the requested id</t>
+  </si>
+  <si>
+    <t>Non-existent id, no matching record exists (NotFoundError "Exercise not found") → operation fails with message "Exercise not found"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -93,31 +88,25 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>id="exercise-001", service resolves {isActive:false}</t>
-  </si>
-  <si>
-    <t>{ success: true, data.isActive: false }</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>id="nonexistent-id", service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Exercise not found" }</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>id="exercise-001", service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>known existing exercise id, the exercise is archived successfully</t>
+  </si>
+  <si>
+    <t>exercise archived successfully, returned data has isActive: false and id matches the requested id</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>non-existent id, no matching record exists (NotFoundError "Exercise not found")</t>
+  </si>
+  <si>
+    <t>operation fails with message "Exercise not found"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -126,22 +115,40 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>isActive boundary</t>
-  </si>
-  <si>
-    <t>isActive=false (archived state)</t>
+    <t>ID length</t>
+  </si>
+  <si>
+    <t>empty string id (length 0): no record can match → operation fails with service error message</t>
+  </si>
+  <si>
+    <t>one-character id that matches an existing record: shortest valid id → exercise archived successfully, returned data has isActive: false</t>
+  </si>
+  <si>
+    <t>one-character id that does not match any record: non-existent → operation fails with service error message</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>isActive=false</t>
-  </si>
-  <si>
-    <t>Service resolves with isActive=false</t>
-  </si>
-  <si>
-    <t>data.isActive=false</t>
+    <t>BVA-1 (len=0)</t>
+  </si>
+  <si>
+    <t>empty string id (""), no matching record exists for this id (NotFoundError)</t>
+  </si>
+  <si>
+    <t>BVA-2 (len=1)</t>
+  </si>
+  <si>
+    <t>one-character id ("a"), a matching exercise record exists with id "a", exercise is archived successfully</t>
+  </si>
+  <si>
+    <t>exercise archived successfully, returned data id is "a" and isActive is false</t>
+  </si>
+  <si>
+    <t>BVA-3 (len=1)</t>
+  </si>
+  <si>
+    <t>one-character id ("a"), no matching record exists for this id (NotFoundError)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -150,34 +157,13 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>Existing exercise id</t>
-  </si>
-  <si>
-    <t>success=true, isActive=false</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>Non-existent id</t>
-  </si>
-  <si>
-    <t>success=false, message from NotFoundError</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
   </si>
   <si>
     <t>Testing</t>
@@ -210,16 +196,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-04</t>
+    <t>CTRL-19</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -735,7 +718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -776,27 +759,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -806,6 +775,135 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -819,19 +917,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -839,13 +937,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>26</v>
@@ -856,16 +954,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,106 +971,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -983,7 +991,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -996,22 +1004,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1019,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1039,19 +1047,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1059,19 +1067,59 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>52</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1099,16 +1147,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1116,45 +1164,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="H2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1163,19 +1211,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>66</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
